--- a/data/trans_camb/P23_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P23_R2-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 2,37</t>
+          <t>-6,03; 2,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,79; -0,32</t>
+          <t>-8,59; 0,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,14; -1,76</t>
+          <t>-11,24; -1,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,4</t>
+          <t>-1,09; 4,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 3,59</t>
+          <t>-2,05; 3,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 0,13</t>
+          <t>-5,06; 0,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,24</t>
+          <t>-2,61; 2,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,7</t>
+          <t>-4,18; 1,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -2,5</t>
+          <t>-7,44; -2,39</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 7,47</t>
+          <t>-16,33; 7,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,16; -1,04</t>
+          <t>-24,1; 0,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,34; -5,18</t>
+          <t>-31,69; -5,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 38,08</t>
+          <t>-7,72; 35,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 30,93</t>
+          <t>-14,23; 32,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 1,38</t>
+          <t>-35,4; 0,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 10,72</t>
+          <t>-10,98; 10,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 3,31</t>
+          <t>-17,99; 5,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,44; -11,67</t>
+          <t>-31,94; -11,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -1,88</t>
+          <t>-8,44; -1,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -3,27</t>
+          <t>-9,97; -3,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,78; -15,3</t>
+          <t>-27,1; -15,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 5,22</t>
+          <t>-1,35; 5,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 2,81</t>
+          <t>-3,19; 3,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,71; -8,76</t>
+          <t>-17,87; -8,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 0,8</t>
+          <t>-3,86; 1,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -1,15</t>
+          <t>-5,88; -0,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-20,7; -13,0</t>
+          <t>-21,8; -13,07</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,08; -4,23</t>
+          <t>-17,91; -4,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,73; -7,53</t>
+          <t>-21,16; -7,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,71; -34,28</t>
+          <t>-58,88; -34,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 16,37</t>
+          <t>-3,82; 18,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 8,79</t>
+          <t>-8,96; 9,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,72; -27,01</t>
+          <t>-52,46; -27,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 2,05</t>
+          <t>-9,55; 2,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,01; -2,93</t>
+          <t>-14,35; -2,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,93; -33,71</t>
+          <t>-53,87; -33,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 5,42</t>
+          <t>-6,45; 5,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,26; -2,8</t>
+          <t>-14,11; -2,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,69; -12,16</t>
+          <t>-22,82; -11,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 8,95</t>
+          <t>-3,77; 9,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 0,7</t>
+          <t>-10,2; 1,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,29; -5,4</t>
+          <t>-15,62; -5,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 4,84</t>
+          <t>-3,66; 4,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,65; -2,89</t>
+          <t>-10,81; -2,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,77; -10,3</t>
+          <t>-17,95; -10,69</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 17,44</t>
+          <t>-18,19; 17,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,31; -8,82</t>
+          <t>-39,47; -8,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,72; -39,02</t>
+          <t>-62,57; -36,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 38,84</t>
+          <t>-12,3; 39,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 2,53</t>
+          <t>-34,42; 4,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,0; -22,8</t>
+          <t>-52,01; -23,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 17,17</t>
+          <t>-11,52; 17,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,86; -9,58</t>
+          <t>-33,64; -9,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,63; -36,78</t>
+          <t>-54,65; -36,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; -0,55</t>
+          <t>-5,6; -0,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,52; -2,84</t>
+          <t>-7,85; -2,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,99; -12,52</t>
+          <t>-21,59; -12,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,77</t>
+          <t>0,37; 4,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,8</t>
+          <t>-0,72; 3,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,26; -4,45</t>
+          <t>-9,97; -4,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,43</t>
+          <t>-1,92; 1,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -0,22</t>
+          <t>-3,43; -0,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,0; -9,05</t>
+          <t>-14,18; -9,25</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,28; -1,43</t>
+          <t>-13,54; -1,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,4; -7,36</t>
+          <t>-19,21; -7,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,02; -31,74</t>
+          <t>-53,38; -32,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 20,24</t>
+          <t>1,58; 19,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 16,09</t>
+          <t>-2,71; 15,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,44; -18,83</t>
+          <t>-39,64; -18,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 4,6</t>
+          <t>-5,83; 4,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,47; -0,7</t>
+          <t>-10,45; -0,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,23; -28,53</t>
+          <t>-43,51; -29,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P23_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P23_R2-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-6,68</t>
+          <t>-7,74</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,66</t>
+          <t>-2,61</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,0</t>
+          <t>-5,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 2,32</t>
+          <t>-6,31; 2,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 0,25</t>
+          <t>-8,79; 0,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,24; -1,67</t>
+          <t>-12,61; -3,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,18</t>
+          <t>-1,02; 4,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,78</t>
+          <t>-2,33; 3,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 0,13</t>
+          <t>-5,22; -0,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,14</t>
+          <t>-2,73; 2,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 1,1</t>
+          <t>-4,19; 0,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; -2,39</t>
+          <t>-7,86; -3,01</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-19,6%</t>
+          <t>-22,7%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-20,28%</t>
+          <t>-19,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-22,41%</t>
+          <t>-23,66%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 7,34</t>
+          <t>-17,35; 6,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 0,6</t>
+          <t>-24,16; 1,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,69; -5,44</t>
+          <t>-35,0; -9,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 35,43</t>
+          <t>-7,7; 36,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 32,0</t>
+          <t>-16,3; 29,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 0,91</t>
+          <t>-36,31; -2,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 10,09</t>
+          <t>-11,54; 10,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 5,21</t>
+          <t>-17,79; 4,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-31,94; -11,45</t>
+          <t>-33,85; -14,19</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-19,68</t>
+          <t>-16,78</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-12,62</t>
+          <t>-10,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-16,31</t>
+          <t>-13,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,44; -1,94</t>
+          <t>-8,37; -1,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,97; -3,21</t>
+          <t>-9,66; -3,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,1; -15,29</t>
+          <t>-20,48; -13,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 5,68</t>
+          <t>-1,22; 5,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,0</t>
+          <t>-3,61; 2,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,87; -8,6</t>
+          <t>-13,23; -7,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,05</t>
+          <t>-3,83; 0,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,88; -0,99</t>
+          <t>-5,82; -1,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,8; -13,07</t>
+          <t>-15,77; -11,46</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-43,31%</t>
+          <t>-36,94%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-37,79%</t>
+          <t>-30,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-41,19%</t>
+          <t>-34,52%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,91; -4,33</t>
+          <t>-17,83; -4,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,16; -7,38</t>
+          <t>-20,52; -7,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,88; -34,44</t>
+          <t>-43,63; -31,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 18,18</t>
+          <t>-3,39; 17,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 9,42</t>
+          <t>-10,18; 9,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,46; -27,07</t>
+          <t>-37,39; -22,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 2,76</t>
+          <t>-9,51; 2,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,35; -2,65</t>
+          <t>-14,27; -2,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,87; -33,55</t>
+          <t>-38,73; -29,88</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-17,47</t>
+          <t>-17,97</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,45</t>
+          <t>-10,75</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-14,21</t>
+          <t>-14,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 5,39</t>
+          <t>-7,03; 4,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,11; -2,82</t>
+          <t>-13,99; -3,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,82; -11,4</t>
+          <t>-23,02; -13,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 9,19</t>
+          <t>-2,74; 9,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 1,02</t>
+          <t>-10,23; 0,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,62; -5,8</t>
+          <t>-15,82; -5,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 4,95</t>
+          <t>-3,47; 5,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,81; -2,96</t>
+          <t>-10,66; -2,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,95; -10,69</t>
+          <t>-18,12; -11,13</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-52,21%</t>
+          <t>-53,7%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-39,03%</t>
+          <t>-40,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-46,78%</t>
+          <t>-48,08%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 17,67</t>
+          <t>-19,63; 15,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,47; -8,82</t>
+          <t>-39,47; -9,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,57; -36,11</t>
+          <t>-63,04; -41,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 39,41</t>
+          <t>-9,31; 39,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 4,15</t>
+          <t>-34,22; 3,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,01; -23,88</t>
+          <t>-52,61; -24,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 17,59</t>
+          <t>-10,84; 18,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,64; -9,98</t>
+          <t>-33,18; -10,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,65; -36,93</t>
+          <t>-56,11; -39,49</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-15,68</t>
+          <t>-14,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,73</t>
+          <t>-5,61</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-11,17</t>
+          <t>-9,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -0,72</t>
+          <t>-5,47; -0,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,85; -2,99</t>
+          <t>-7,61; -3,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,59; -12,89</t>
+          <t>-16,56; -11,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,65</t>
+          <t>0,22; 4,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,58</t>
+          <t>-0,84; 3,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,97; -4,39</t>
+          <t>-7,7; -3,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,4</t>
+          <t>-1,93; 1,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; -0,26</t>
+          <t>-3,4; -0,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -9,25</t>
+          <t>-11,46; -8,42</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-39,34%</t>
+          <t>-35,73%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-27,4%</t>
+          <t>-22,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-34,82%</t>
+          <t>-30,85%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,54; -1,82</t>
+          <t>-13,4; -1,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,21; -7,8</t>
+          <t>-18,45; -7,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,38; -32,9</t>
+          <t>-40,34; -30,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 19,81</t>
+          <t>0,85; 20,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 15,57</t>
+          <t>-3,32; 14,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,64; -18,56</t>
+          <t>-29,88; -15,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 4,45</t>
+          <t>-5,8; 4,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,45; -0,77</t>
+          <t>-10,33; -0,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,51; -29,34</t>
+          <t>-34,97; -26,94</t>
         </is>
       </c>
     </row>
